--- a/results/Int Task Remove ACC -0.6/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.6/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.532030744710201e-06</v>
+        <v>0.0009639962453649476</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0007080727046616688</v>
+        <v>-0.0008813013305691043</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0002622809707492355</v>
+        <v>-0.002283587146877352</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001220799942565028</v>
+        <v>4.142256233832459e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0003777125693265905</v>
+        <v>-0.001618294219054222</v>
       </c>
       <c r="H3" t="n">
-        <v>-9.02144120684033e-06</v>
+        <v>0.002606964635276377</v>
       </c>
       <c r="I3" t="n">
-        <v>5.711251625116431e-05</v>
+        <v>0.0002164826004745235</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007209709097736452</v>
+        <v>-0.0001585010413665446</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01868200246166937</v>
+        <v>0.01522395843459833</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02046875110278732</v>
+        <v>0.01939862530147204</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.001145233689447887</v>
+        <v>-0.002491177288434171</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0003996718756437943</v>
+        <v>-0.002447846693109002</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001296831773117191</v>
+        <v>0.001522480100241273</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003939290386072343</v>
+        <v>0.001087207684929653</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.009536305817816089</v>
+        <v>0.008370079015722492</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0009243091136222645</v>
+        <v>0.0001942180022558682</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004364372000213135</v>
+        <v>-0.0003927094549189336</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0008752194855955666</v>
+        <v>-0.001045897598586741</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0002701376449093951</v>
+        <v>0.0007631781359197399</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001881392526729753</v>
+        <v>-3.578311203569218e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0002788568837992099</v>
+        <v>0.001355414292590738</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.002745328973896355</v>
+        <v>-0.002478515240435168</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001320512203068349</v>
+        <v>0.0004487685037275624</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.000817053426942025</v>
+        <v>0.001529149503636177</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008452758525364368</v>
+        <v>0.001004055833839668</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0002974866437528467</v>
+        <v>-0.0004016116885413012</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.004826847661106256</v>
+        <v>0.004957354744793729</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.003815131530982718</v>
+        <v>-0.001003088707402757</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.004375160648034527</v>
+        <v>-0.002974236731234121</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.003139261517543819</v>
+        <v>-0.002213572152170662</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0002420462756468333</v>
+        <v>0.0002018755486011448</v>
       </c>
       <c r="AH3" t="n">
-        <v>9.460366168974831e-05</v>
+        <v>-0.0003028611466035991</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.003515050479915957</v>
+        <v>-0.001439557811811054</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.005769612200747335</v>
+        <v>-0.001005409614695944</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0003621974758211587</v>
+        <v>-0.0003197833847787657</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0004511977384926802</v>
+        <v>0.0005472405319999795</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.00122518002250241</v>
+        <v>0.001165232344645232</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.001483359268716604</v>
+        <v>-0.00273094160100918</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0003167284583872332</v>
+        <v>-0.0002617010476665571</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.001391233180372278</v>
+        <v>0.0009329657668199943</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.002752376304311004</v>
+        <v>-0.001161149402577953</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0006194101103289251</v>
+        <v>-0.0008870554704851985</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.001864842437516948</v>
+        <v>-0.005552491729149084</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.001279624863136632</v>
+        <v>0.003590510882148141</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.000344924195453683</v>
+        <v>8.307239240341832e-05</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.0006756340234604174</v>
+        <v>-0.0009887013230180264</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.0004731876004287595</v>
+        <v>-0.0001656906134493807</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.001827703642811943</v>
+        <v>-0.001104770221788266</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.0002708465428462448</v>
+        <v>0.0009546949588782903</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.005334464618719964</v>
+        <v>-0.00431281117002638</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.001066001655714017</v>
+        <v>-0.002976768513301983</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0003230779923332982</v>
+        <v>-2.250074356882179e-05</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.890861575980843e-05</v>
+        <v>-0.0004008561646730635</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0007264047142463724</v>
+        <v>-0.0001270114508997633</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.001674055523738446</v>
+        <v>-0.004491603625328493</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.0005294248327769292</v>
+        <v>-0.003597906598300813</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.0005355766231454185</v>
+        <v>-0.000337318591404131</v>
       </c>
       <c r="BJ3" t="n">
-        <v>7.968406063535983e-05</v>
+        <v>0.0002997867691300781</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.002556227123152464</v>
+        <v>-0.002484436614454823</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.0001334872875847293</v>
+        <v>0.0002033155228806849</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.001747519913219221</v>
+        <v>-0.001221054727438935</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.004103562180897252</v>
+        <v>-0.006917374533324608</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.001418302501863433</v>
+        <v>-0.001232612325984429</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.002109865469938017</v>
+        <v>-0.001078262301133402</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.057696873161044e-05</v>
+        <v>5.196413711436086e-05</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.001657817006608565</v>
+        <v>0.0007305295289385928</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0006854938088563468</v>
+        <v>0.0005912972005703542</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0005690503921190871</v>
+        <v>0.0001716203249107629</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.006018603812212153</v>
+        <v>0.004855582339991646</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.000646268030904198</v>
+        <v>0.0002165025578541191</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.001928076981662075</v>
+        <v>-0.0008291865545854161</v>
       </c>
       <c r="BX3" t="n">
-        <v>-9.219213902641465e-05</v>
+        <v>-0.0001128543049971209</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0008803391949909811</v>
+        <v>-0.0004205163543510826</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0003388569983630341</v>
+        <v>-5.151947105331175e-05</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.293005283427908e-06</v>
+        <v>3.252870559973364e-05</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0003581978812164444</v>
+        <v>0.0003484106702621559</v>
       </c>
       <c r="CC3" t="n">
-        <v>-6.238569743754917e-05</v>
+        <v>0.0004771546953128602</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.000424403183023876</v>
+        <v>-3.482711168456662e-08</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0001273398942793313</v>
+        <v>0.0002014226745990388</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.000403791084286591</v>
+        <v>-0.0009836439527998197</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.001358722283191143</v>
+        <v>-0.0004164293610677893</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.000301608798583357</v>
+        <v>-0.00054307406000336</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0003089157895993078</v>
+        <v>-0.001063159543078647</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.00106085755316546</v>
+        <v>0.002537235216789772</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0004961371526909264</v>
+        <v>-0.000314035706353103</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004734756940210705</v>
+        <v>0.006158018751301914</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005751893716959387</v>
+        <v>0.007566073344211744</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008140941376948888</v>
+        <v>0.008914551131311685</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002680087490240006</v>
+        <v>0.004187028503459757</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003933281434948512</v>
+        <v>0.005284349989996818</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00525404429097317</v>
+        <v>0.003557382260075537</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0004910476110526482</v>
+        <v>0.0003196699632867911</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004331279501563317</v>
+        <v>0.003345924191040066</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01408384938135166</v>
+        <v>0.01723814228892043</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01409964497549429</v>
+        <v>0.0145978586112376</v>
       </c>
       <c r="M4" t="n">
-        <v>0.004697954050725565</v>
+        <v>0.00391369652212566</v>
       </c>
       <c r="N4" t="n">
-        <v>0.005216043817879269</v>
+        <v>0.005761623255657563</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007741540023502007</v>
+        <v>0.00767940354306313</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01062775767673665</v>
+        <v>0.01446122088126305</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01115995197094194</v>
+        <v>0.01135530050167351</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002410690813981571</v>
+        <v>0.004795547079924648</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003645823385537819</v>
+        <v>0.004277928788637139</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002976363622502789</v>
+        <v>0.004098139076356314</v>
       </c>
       <c r="U4" t="n">
-        <v>0.003063310115057462</v>
+        <v>0.004124119142655661</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0005988390143796265</v>
+        <v>0.0002499877019309272</v>
       </c>
       <c r="W4" t="n">
-        <v>0.007848068955551278</v>
+        <v>0.008300487034029724</v>
       </c>
       <c r="X4" t="n">
-        <v>0.003370807056700276</v>
+        <v>0.005972698315102767</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001947977412878326</v>
+        <v>0.002219017265396499</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001961425556744042</v>
+        <v>0.00214704323839877</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003664304756010049</v>
+        <v>0.003316742141512598</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0007327515902606168</v>
+        <v>0.0007204107927329923</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.006364118691243866</v>
+        <v>0.004531708801358816</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.007950264971072677</v>
+        <v>0.006481596503102617</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.005976088074733543</v>
+        <v>0.003904995787324618</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.006408713358431336</v>
+        <v>0.00659213544663515</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0007034384564001542</v>
+        <v>0.0007288654478063543</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.000357316410766697</v>
+        <v>0.00104903612063304</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.005720755578438284</v>
+        <v>0.006146013489207814</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.006143619465073398</v>
+        <v>0.005225387562335653</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001574439374891313</v>
+        <v>0.0009379055980965041</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.001348555742418588</v>
+        <v>0.001448488020927503</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.003448093622472392</v>
+        <v>0.00254994119377941</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.003603918313739893</v>
+        <v>0.004250519687096226</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001026201972632928</v>
+        <v>0.001278062973696387</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.003384981545976442</v>
+        <v>0.004171049469669365</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.003652245857459374</v>
+        <v>0.005099442900233194</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.003638451812530669</v>
+        <v>0.003829769015530859</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.006105881389318725</v>
+        <v>0.005451906811112562</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.005499658999589992</v>
+        <v>0.004392779820680548</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.004186258704875789</v>
+        <v>0.00311839956836508</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.00595666417758879</v>
+        <v>0.00289870402058104</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0010064606172487</v>
+        <v>0.0006884401779824563</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.003350957866653315</v>
+        <v>0.003205433160685491</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.01005407335400721</v>
+        <v>0.006913447464827564</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.008755221559332808</v>
+        <v>0.008802572171499084</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.005573470940817854</v>
+        <v>0.007856617389025097</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0007324462058398622</v>
+        <v>0.001202654519979133</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.001641749650640678</v>
+        <v>0.0005442364417704333</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001232007112507837</v>
+        <v>0.0009688503072597602</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.008766553834902577</v>
+        <v>0.01176794339193323</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.008729111476759871</v>
+        <v>0.008720918982876608</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.001378686821734524</v>
+        <v>0.0009807985823828789</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.002384414505593602</v>
+        <v>0.002794744556205476</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.006318711295323238</v>
+        <v>0.005930190458138879</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0009751483080890029</v>
+        <v>0.0009617164865105938</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.003276028895951403</v>
+        <v>0.003605188604390023</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.01078920266292488</v>
+        <v>0.01026871895989954</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.003333158732172535</v>
+        <v>0.004236522333958547</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.004644353381402099</v>
+        <v>0.002968289459073425</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0004825759772100719</v>
+        <v>0.0003101605106460736</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.004685504264775916</v>
+        <v>0.003195369607858664</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.002516934598783326</v>
+        <v>0.002281861192647691</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001803844956104515</v>
+        <v>0.001555328787841752</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.008699583887499017</v>
+        <v>0.009217780809423738</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003263749831987992</v>
+        <v>0.001841707228489886</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.004373044998538075</v>
+        <v>0.004538243483584046</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0004532509473664568</v>
+        <v>0.0004753019286106294</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.002037517479315279</v>
+        <v>0.0007874036954119699</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.001757307898912918</v>
+        <v>0.001099505204575732</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.274070651097391e-05</v>
+        <v>6.610583510693493e-05</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001202091793416165</v>
+        <v>0.0008876008348542529</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.002380495951076382</v>
+        <v>0.004850295094513423</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.001342080704580755</v>
+        <v>6.954934201532088e-05</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0016248000460594</v>
+        <v>0.0009979810864590361</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.003826623748861037</v>
+        <v>0.002302265556511364</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.004353556119586773</v>
+        <v>0.003277096681581819</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001937824379523465</v>
+        <v>0.002124820366960426</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.002397587026439181</v>
+        <v>0.003162559281692283</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.006728202751527081</v>
+        <v>0.003966343796330474</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.003083658873017064</v>
+        <v>0.002200535815203049</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.006483126110124393</v>
+        <v>-0.007692307692307654</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.006626332469029117</v>
+        <v>-0.01126476519734942</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0142898300201671</v>
+        <v>-0.02100259291270524</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.002632403635224101</v>
+        <v>-0.005654233274126686</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002772043644942546</v>
+        <v>-0.012267767620171</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.004399375975039</v>
+        <v>-0.002567237163814218</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0007800312012480215</v>
+        <v>-8.643042350905405e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.006008328375966709</v>
+        <v>-0.004387339392040124</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.002016709881878442</v>
+        <v>-0.01040046096225868</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.005387496398732372</v>
+        <v>-0.008268510515701478</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01000592066311433</v>
+        <v>-0.008095649668683336</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.009230315541138368</v>
+        <v>-0.01616248919619702</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.01287813310285221</v>
+        <v>-0.009276865456640693</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.00786516853932585</v>
+        <v>-0.02535292422932868</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.01064582718961963</v>
+        <v>-0.007578885284576764</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.004180967238689525</v>
+        <v>-0.003788102989050013</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.002246489859594392</v>
+        <v>-0.003552397868561275</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.008496151568975773</v>
+        <v>-0.008762581409117809</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.003572457505041804</v>
+        <v>-0.004580812445980953</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.001094998520272306</v>
+        <v>-0.0003255401006214798</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01131741821397</v>
+        <v>-0.006749555950266417</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.008210890233362167</v>
+        <v>-0.01391575663026522</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.001222493887530529</v>
+        <v>-0.003153551429413459</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.00251553714116608</v>
+        <v>6.112469437650204e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.004647720544701051</v>
+        <v>-0.003881418092909594</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0002592912705272177</v>
+        <v>-0.001650456822870594</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.0056525599289731</v>
+        <v>-0.004494382022471865</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.02297217288336299</v>
+        <v>-0.01557134399052693</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.01811722912966256</v>
+        <v>-0.009881878421204216</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.01604523227383859</v>
+        <v>-0.01347893915756631</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.0006267627702914669</v>
+        <v>-0.0006216696269982003</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.0002948982601003181</v>
+        <v>-0.001222493887530585</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01616042465349459</v>
+        <v>-0.01587438778450011</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.02089994079336891</v>
+        <v>-0.008940201302545848</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.003243880861102977</v>
+        <v>-0.002036979003447215</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.001090480400825256</v>
+        <v>-0.001498127340823929</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.004431314623338234</v>
+        <v>-0.00204202426753477</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.009443765281173544</v>
+        <v>-0.0090238867590681</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.001865008880994734</v>
+        <v>-0.002292176039119864</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.00479431784551646</v>
+        <v>-0.005324211778703181</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.009295441089402079</v>
+        <v>-0.01086142322097374</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.005906078939786808</v>
+        <v>-0.007519500780031196</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.01138000576202827</v>
+        <v>-0.01796549672813803</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.005073349633251778</v>
+        <v>-0.001566906925728617</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.0069720541630654</v>
+        <v>-0.004450015669069274</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.009392106021319513</v>
+        <v>-0.006972054163065377</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.003037452079032776</v>
+        <v>-0.00106968215158928</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.009407254497198514</v>
+        <v>-0.007058484586574432</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.01630787378354472</v>
+        <v>-0.01426101987899736</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.02633246902909825</v>
+        <v>-0.02376836646499565</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.01110764430577224</v>
+        <v>-0.01307980409104001</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.001036116044997093</v>
+        <v>-0.0010904804008252</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.004158065467413774</v>
+        <v>-0.001120613388380964</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.00349215744303053</v>
+        <v>-0.002101835405565422</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.01607605877268802</v>
+        <v>-0.03295880149812732</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01927398444252378</v>
+        <v>-0.02515125324114083</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.00380418755529347</v>
+        <v>-0.002256345973049212</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.004305514597463933</v>
+        <v>-0.004180967238689548</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.01685393258426967</v>
+        <v>-0.01541342552578504</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.002270716602772116</v>
+        <v>-0.001528117359413228</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.009259805367148377</v>
+        <v>-0.005358686257562606</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.027945836934601</v>
+        <v>-0.03465859982713913</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.008522559716897726</v>
+        <v>-0.0075482569864592</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.003071137574428129</v>
+        <v>-0.004230648699467265</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.0004278728606356474</v>
+        <v>-0.0004164187983343059</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.003807257584770984</v>
+        <v>-0.003184901209082813</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.003315571343990598</v>
+        <v>-0.00159824506424322</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.00191683869065179</v>
+        <v>-0.001457465794170143</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.003751846381093038</v>
+        <v>-0.006262924667651415</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.004627173592690881</v>
+        <v>-0.003575794621026951</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.003515509601181666</v>
+        <v>-0.006581009088060186</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.00120908286641116</v>
+        <v>-0.001191931540342339</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.001592450604541507</v>
+        <v>-0.001746595618709257</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.001754935756816101</v>
+        <v>-0.002152886115444619</v>
       </c>
       <c r="CA5" t="n">
-        <v>-2.947244326555465e-05</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.0006112469437652313</v>
+        <v>-0.001128172986524634</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.00538780343398465</v>
+        <v>-0.004617784711388462</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.004244031830238759</v>
+        <v>-0.0001477104874446078</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.004479811376363141</v>
+        <v>-0.001060842433697362</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.007755824240637044</v>
+        <v>-0.003996447602131447</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.009171335889118315</v>
+        <v>-0.005629236663719383</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.004656646035956435</v>
+        <v>-0.0054524020041261</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.004492979719188772</v>
+        <v>-0.006365054602184094</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.005246094901267373</v>
+        <v>-0.004606706361642132</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.005897965202005351</v>
+        <v>-0.003370786516853885</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.002028988351010841</v>
+        <v>-0.002909012469061131</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.004155036818118205</v>
+        <v>-0.005383136997469218</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.002201911665805242</v>
+        <v>-0.004388430894612359</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0002890669861642936</v>
+        <v>-0.003977135968433815</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.002587489054488676</v>
+        <v>-0.003159921771552107</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.002946895627675875</v>
+        <v>0.001447472439793856</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0001255408000496588</v>
+        <v>-5.175994271931217e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.001802996055653231</v>
+        <v>-0.002011975100030896</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01155103593131288</v>
+        <v>0.002954224708457468</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01544544907906436</v>
+        <v>0.01013180171967092</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.003527580497108998</v>
+        <v>-0.004460400592372826</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.003008743551872891</v>
+        <v>-0.003022118093179155</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.00154522163893831</v>
+        <v>-0.002984608899534994</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.00632095263488068</v>
+        <v>-0.008755224646583168</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.005209133313542025</v>
+        <v>0.002099388563045229</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.002679769238844506</v>
+        <v>-0.002379128162159516</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.00155113351966808</v>
+        <v>-0.00250437163377836</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.00137960630801412</v>
+        <v>-0.003654221249204895</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.001630757683856168</v>
+        <v>-0.001064263582677063</v>
       </c>
       <c r="V6" t="n">
-        <v>7.436049970246939e-06</v>
+        <v>-0.0001403861811548002</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.004797423106630108</v>
+        <v>-0.004738749776982739</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.005375079582873952</v>
+        <v>-0.005946242106436872</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0001941197818034923</v>
+        <v>-0.001065377682762136</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.000416916462315739</v>
+        <v>0.0003467285980476187</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.001479315020075839</v>
+        <v>-0.001239629244698362</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0001539323020483568</v>
+        <v>-0.0008658930626887855</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.001891510517196765</v>
+        <v>0.002656352202183551</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.005131423565812176</v>
+        <v>-0.004360845362395113</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.006371424897735525</v>
+        <v>-0.005714954708312667</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.006616889056634045</v>
+        <v>-0.005536469235045488</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0002662217483761414</v>
+        <v>-0.0002410048782389068</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0001477410964858289</v>
+        <v>-0.001139438083990193</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.00393697096198454</v>
+        <v>-0.003033587330304405</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.006722770039201967</v>
+        <v>-0.0058647678465578</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0001996058722240873</v>
+        <v>-0.0008941078294041893</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.0002291533579312471</v>
+        <v>-0.0006100481542441527</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0001671290100922595</v>
+        <v>-0.001116018947923178</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.003146812723519016</v>
+        <v>-0.005537416889958189</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0009547868153258116</v>
+        <v>-0.0009292977978877319</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.001201959932096733</v>
+        <v>-0.001937005151114601</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.005041155972338712</v>
+        <v>-0.003901639184077668</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.0001477044815630546</v>
+        <v>-0.003610469042459408</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.005718367879754882</v>
+        <v>-0.006458930826149562</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.001198750626392206</v>
+        <v>-0.0002655788604205761</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.001404655751345279</v>
+        <v>-0.002839519581940772</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.004581173385997781</v>
+        <v>-0.002336048099311294</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0005725577337700266</v>
+        <v>-0.0008031805729056846</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.003305155835391929</v>
+        <v>-0.002565340019001333</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.000806750438407483</v>
+        <v>-0.001628919949062149</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.00694904373013753</v>
+        <v>-0.003841967695804197</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.001486683341812611</v>
+        <v>-0.008713464301655746</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0001419535856095139</v>
+        <v>-0.0009692851802420327</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0001986439707757026</v>
+        <v>-0.0008555515246885026</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.001071527444090187</v>
+        <v>-0.0006443593981127233</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.006168473397738673</v>
+        <v>-0.007173854102725963</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.002114177782270204</v>
+        <v>-0.005685444244730045</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.0007763017999130511</v>
+        <v>-0.0005853346830050233</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.0005066740821114441</v>
+        <v>-0.001626834464414539</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.00449416723402162</v>
+        <v>-0.004924998299076036</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0006215250710033038</v>
+        <v>-0.0003747653498837905</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.003036190268275618</v>
+        <v>-0.003877708544879929</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.00977639182902236</v>
+        <v>-0.007269255206420897</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.002562869960788411</v>
+        <v>-0.002782571934053568</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.001925389343813463</v>
+        <v>-0.003429310827152845</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0.0002590180600375608</v>
+        <v>-0.0001695926352970695</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.001923053309401085</v>
+        <v>-0.001021023726745524</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.0005938237021844206</v>
+        <v>-0.001172805532910948</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0006722532034903167</v>
+        <v>-0.001025595608176447</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.0005279882779224948</v>
+        <v>-0.001367626596315133</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.003761824595529934</v>
+        <v>-0.00054990343575671</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.001290431570370989</v>
+        <v>-0.004280789596558643</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.0001146088019559705</v>
+        <v>-0.0001686386711570481</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.0001306438768766182</v>
+        <v>-0.0008698803363178325</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.00120211447767036</v>
+        <v>-0.0008182679355421107</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0003989363446047667</v>
+        <v>-0.000155377982387292</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.0003865978916043289</v>
+        <v>-0.002292881741630351</v>
       </c>
       <c r="CD6" t="n">
         <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-5.8221316617596e-05</v>
+        <v>-0.0005026800385557667</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.002890514677205697</v>
+        <v>-0.002251708344617426</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.003207692543192791</v>
+        <v>-0.002175063163942878</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0009609536977846472</v>
+        <v>-0.0005978933396626862</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.0006249270394894952</v>
+        <v>-0.002703197670336196</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.003332104234032163</v>
+        <v>2.672622072056596e-05</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.0006132214656255158</v>
+        <v>-0.001302125619660649</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.000681191297747108</v>
+        <v>0.0002348110481877053</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.002308705763309565</v>
+        <v>-0.001569891473294138</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002741971190243331</v>
+        <v>-0.002418549770935341</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0005481289142453161</v>
+        <v>0.0007149975953894993</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.001486942332162233</v>
+        <v>-0.001275582557244892</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.001476107196642717</v>
+        <v>0.002641266383435192</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001771618403577257</v>
+        <v>0.0001628299777326536</v>
       </c>
       <c r="J7" t="n">
-        <v>-5.920663114269974e-05</v>
+        <v>-0.0007791570096420341</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01648887472675688</v>
+        <v>0.0152447991562694</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01914475607574372</v>
+        <v>0.02272442573668364</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0005687507313849205</v>
+        <v>-0.003159486128591909</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001304930271484539</v>
+        <v>-0.001977435418386697</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0001625339933021108</v>
+        <v>0.001000047963709494</v>
       </c>
       <c r="P7" t="n">
-        <v>0.004963746732990476</v>
+        <v>0.006740789171796763</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.007562715239265705</v>
+        <v>0.007613437414074137</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.001493785385847618</v>
+        <v>-0.001122258987020081</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.001211880933776116</v>
+        <v>-0.001561550102453518</v>
       </c>
       <c r="T7" t="n">
-        <v>9.216610303911522e-05</v>
+        <v>-0.0004433937478989791</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.000503440018960144</v>
+        <v>-0.0002829106581027641</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0003962016291952419</v>
+        <v>-6.141227835667617e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.263998672443312e-05</v>
+        <v>-0.002728987170998049</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.001565331578780416</v>
+        <v>-0.0007808914359533903</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001247221404034965</v>
+        <v>0.0009294698265615853</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0002367130350093782</v>
+        <v>0.0008429706271647851</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0008843645081556439</v>
+        <v>0.001139979082647396</v>
       </c>
       <c r="AB7" t="n">
-        <v>-4.446665454247989e-05</v>
+        <v>-0.0005632747445589225</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.003838434075517738</v>
+        <v>0.005611851611967233</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.003217250833743851</v>
+        <v>0.0008140338514493141</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.002787803092372687</v>
+        <v>-0.003020404652755837</v>
       </c>
       <c r="AF7" t="n">
-        <v>5.866626963757504e-05</v>
+        <v>-0.002469533981653182</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.959455460195271e-05</v>
+        <v>0.0002115169488520474</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.65408612135709e-05</v>
+        <v>-0.0007352826861429297</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.002039873960713745</v>
+        <v>-0.0001445019500057265</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.004952288069984784</v>
+        <v>0.00183063493840579</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0004360696587321577</v>
+        <v>-0.0002368177636013546</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0001410216233155293</v>
+        <v>0.0006048816291774784</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0008917227599276266</v>
+        <v>0.00118765223282491</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.0007642692709185384</v>
+        <v>-0.00258546180669384</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.0004881794077049861</v>
+        <v>-0.000425686546006826</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.001836987782689814</v>
+        <v>0.001259708746420646</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.002517093787199798</v>
+        <v>-4.410436843140799e-05</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0004599235349992903</v>
+        <v>-0.0002785278510276934</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.003021889265526301</v>
+        <v>-0.003347427948388815</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.0004535080305486716</v>
+        <v>0.002808320086576771</v>
       </c>
       <c r="AV7" t="n">
-        <v>-2.145991287351711e-05</v>
+        <v>0.000974578094321893</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0006656697164601432</v>
+        <v>-0.0007080126619308013</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.0002811702798453775</v>
+        <v>-0.0002115208419952275</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.00160702979843334</v>
+        <v>-0.001202499412273733</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0003706271228907099</v>
+        <v>0.002058553847210404</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.002550929623391851</v>
+        <v>-0.001688264420471353</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.000279996532658594</v>
+        <v>-0.00451406037442929</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0003410477866712503</v>
+        <v>-0.0001864348322276277</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0002068566038726349</v>
+        <v>-0.0004001250682426516</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.0002076658859362368</v>
+        <v>-7.487549342165555e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.00168745148909793</v>
+        <v>-0.003153190308541454</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.001197399176335878</v>
+        <v>-0.002013702506424675</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0.0004670847583723492</v>
+        <v>-0.0005021125066098809</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0002955521176717768</v>
+        <v>3.311510479314672e-06</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.001071970751690687</v>
+        <v>-0.002173206392948351</v>
       </c>
       <c r="BL7" t="n">
-        <v>-3.178956814910428e-05</v>
+        <v>0.0003108348134991112</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0004251610873477196</v>
+        <v>-0.001666117227624475</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.001176650366748167</v>
+        <v>-0.005020120453831006</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.0010808481991186</v>
+        <v>-0.002462408665764459</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.00134303629846832</v>
+        <v>-0.001255803513201714</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-7.627431534043549e-05</v>
+        <v>4.535962448922737e-05</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0007103481591713645</v>
+        <v>-0.0002063904776382519</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.000742344141179041</v>
+        <v>-5.451564322682119e-05</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0002822881302503244</v>
+        <v>-0.0001624647719697114</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.005329379389821048</v>
+        <v>0.003766327815708287</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.000477287255365777</v>
+        <v>0.0002070395547521531</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0005768066005708616</v>
+        <v>-0.001431914749214996</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>-9.054476965726921e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0004448393766599667</v>
+        <v>-0.0001190778507201451</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.0001028872163615358</v>
+        <v>-2.964701171498385e-05</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-4.664238122592534e-06</v>
+        <v>0.0004922897854564678</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0.0001625082288309487</v>
+        <v>0.0001382230804420403</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.0002078571883929237</v>
+        <v>-3.391895784749522e-05</v>
       </c>
       <c r="CF7" t="n">
-        <v>-7.397767988718274e-05</v>
+        <v>-0.001509345008698837</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0002382567526363289</v>
+        <v>-0.0005708668288901542</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0002247177937221512</v>
+        <v>-0.0002702347793923088</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0003064420933727718</v>
+        <v>-0.001284382866706585</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0.0003741975317773649</v>
+        <v>0.002995005588519417</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0004741133465563207</v>
+        <v>-0.0005124755267028325</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0005625977363097168</v>
+        <v>0.00338355221250414</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000714173656890213</v>
+        <v>0.005890723424200078</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001822259148545582</v>
+        <v>-0.0001399850042689332</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002375794005955429</v>
+        <v>0.003431433587911328</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001893369552055568</v>
+        <v>0.001801665226284954</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0007985498778004252</v>
+        <v>0.003877305561111358</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0003425860975129341</v>
+        <v>0.0003668884455158616</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002064439487908013</v>
+        <v>0.0003772680501600512</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02609115187608868</v>
+        <v>0.02354262849959241</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0244860470636475</v>
+        <v>0.0264202491822163</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002096393750402351</v>
+        <v>0.0008739767704343869</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001886572985644919</v>
+        <v>0.000380562170038376</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003707920749592866</v>
+        <v>0.004828046344226905</v>
       </c>
       <c r="P8" t="n">
-        <v>0.008583692850589179</v>
+        <v>0.01025080817625256</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0119614854798165</v>
+        <v>0.01423043437629924</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001006263041798031</v>
+        <v>0.001011031039339316</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0009666359705352095</v>
+        <v>-0.000732708043052005</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0005217960552163115</v>
+        <v>0.001417296221548611</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0011447132113999</v>
+        <v>0.002938094988459597</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0005133532158140997</v>
+        <v>2.210433244918264e-05</v>
       </c>
       <c r="W8" t="n">
-        <v>0.005323194697542267</v>
+        <v>0.006923904597497893</v>
       </c>
       <c r="X8" t="n">
-        <v>5.563871171724577e-05</v>
+        <v>0.002262412498170524</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003065961977236647</v>
+        <v>0.002222783364484044</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002738240564105288</v>
+        <v>0.001526340932098991</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002526194599472115</v>
+        <v>0.003153255565356325</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0005979733675866933</v>
+        <v>0.0002212521022935648</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.008843645112280186</v>
+        <v>0.00838733800334856</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.002373871544103823</v>
+        <v>0.003503890258282927</v>
       </c>
       <c r="AE8" t="n">
-        <v>-6.595937630284875e-05</v>
+        <v>0.0001481155914060533</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.001219133001562522</v>
+        <v>0.00143366119146866</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0005843830421866314</v>
+        <v>0.0004083259155897162</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0002196627190930195</v>
+        <v>0.000368518096533435</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0.0002299060966931498</v>
+        <v>0.002109846588941475</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.002579252724545283</v>
+        <v>0.002686947096710687</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0007702849631710362</v>
+        <v>0.000170928098119813</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0008747510020241961</v>
+        <v>0.001487230705551404</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.003742975214403552</v>
+        <v>0.003304898328912498</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0008329362180209911</v>
+        <v>-0.0002569449619891972</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0001940150532114854</v>
+        <v>0.0008391985680014119</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.004166443863671274</v>
+        <v>0.00208197525759046</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.0003646297746618399</v>
+        <v>0.001802435146615433</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.002271518446944737</v>
+        <v>0.00218915316398762</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.002780403171510468</v>
+        <v>-0.002076666817561362</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.001528069986571015</v>
+        <v>0.006961547258370174</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.002361266868549824</v>
+        <v>0.001778533210293937</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.002041436262617111</v>
+        <v>0.0002580097954397814</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.000170842092717044</v>
+        <v>0.0002895512184577315</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0003713909739953225</v>
+        <v>0.0005972095930447286</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.005084198610475157</v>
+        <v>0.004136143449309296</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0.001019612483612589</v>
+        <v>0.000502703236875296</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.001192071734595473</v>
+        <v>0.002646587982646245</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0006971557436493026</v>
+        <v>0.0002622156198545084</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0007666414386034215</v>
+        <v>3.182823942173008e-05</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.326672684688675e-18</v>
+        <v>0.0005525876207462449</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.00437285170079323</v>
+        <v>0.003004170263229003</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.005582947129158872</v>
+        <v>0.0004172800754033422</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0001970161671219772</v>
+        <v>-0.0001163995933464723</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.00122946356575398</v>
+        <v>0.002556187267863208</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.001102371501058591</v>
+        <v>-2.495221881134162e-05</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0004991048429549339</v>
+        <v>0.0009050054243351369</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0002693278697620732</v>
+        <v>0.0003976866384510252</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0003324666252546848</v>
+        <v>-0.001600458606349792</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0005139418528793182</v>
+        <v>0.0009919400981751704</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.006423605434448244</v>
+        <v>-0.0001800341676588157</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0002654084340902113</v>
+        <v>0.0001530465713010798</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.005121862345758196</v>
+        <v>0.00126063402920758</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.001414859795563228</v>
+        <v>0.001184905515270518</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.00160012486365953</v>
+        <v>0.0005918888175373615</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.00935591127669709</v>
+        <v>0.00843115818624416</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001657748437875312</v>
+        <v>0.0008870674968971204</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.006300730680912622</v>
+        <v>0.002347709398220321</v>
       </c>
       <c r="BX8" t="n">
-        <v>7.790945030824447e-05</v>
+        <v>-7.38552437223039e-06</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0008355411491320908</v>
+        <v>0.0001484202619660424</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.002046957530835497</v>
+        <v>0.0009729503994638734</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>4.423473901504771e-05</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0006007229377939405</v>
+        <v>0.0007619623569961793</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0005560808455528088</v>
+        <v>0.001517319504466352</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0003592442226908965</v>
+        <v>0.0007455994017414481</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.002059782279230868</v>
+        <v>0.0005932357022759432</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.001168268733907615</v>
+        <v>0.0007760144676281194</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0009958774480352593</v>
+        <v>-0.0001113294230893319</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001457112157241922</v>
+        <v>-8.301945444242346e-05</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.002547521700978911</v>
+        <v>0.004170795613953446</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.001186177350640777</v>
+        <v>1.48497344140075e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01202475685234299</v>
+        <v>0.01400766735476264</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01379310344827582</v>
+        <v>0.009297971918876735</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01762452107279689</v>
+        <v>0.01582670203359861</v>
       </c>
       <c r="F9" t="n">
-        <v>0.006749189507810149</v>
+        <v>0.005710886377156432</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008871205422929495</v>
+        <v>0.005709828393135741</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01382257589154138</v>
+        <v>0.008964907107048115</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0006246281975014756</v>
+        <v>0.0009158050221565684</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00872384320660179</v>
+        <v>0.007932763196697178</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04588859416445619</v>
+        <v>0.04538756262894197</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04977895667550836</v>
+        <v>0.04087827880931334</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004942290618526158</v>
+        <v>0.002781888132583587</v>
       </c>
       <c r="N9" t="n">
-        <v>0.006572354848216855</v>
+        <v>0.005629236663719461</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0166814028882994</v>
+        <v>0.01488358384910112</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0229625223081499</v>
+        <v>0.02165377751338488</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02791040377247269</v>
+        <v>0.03152885187388458</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002996254681647925</v>
+        <v>0.01263650546021841</v>
       </c>
       <c r="S9" t="n">
-        <v>0.009843796050692554</v>
+        <v>0.0110226937813145</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001844140392623406</v>
+        <v>0.005337658507814836</v>
       </c>
       <c r="U9" t="n">
-        <v>0.006984969053934531</v>
+        <v>0.009879091713358934</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0008863080684596957</v>
+        <v>0.0005308168681804948</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0118254202300206</v>
+        <v>0.01654379239162492</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0008271787296898036</v>
+        <v>0.003929098966026568</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003993759750390002</v>
+        <v>0.003037452079032765</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003271861986912527</v>
+        <v>0.0072386895475819</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.006573468173706121</v>
+        <v>0.006292466765140292</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002004126142057128</v>
+        <v>0.0005948839976204434</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01594459180666074</v>
+        <v>0.01029641185647425</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.003088923556942291</v>
+        <v>0.005308168681804814</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.001754907792980365</v>
+        <v>0.002349791790600808</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.001953818827708664</v>
+        <v>0.009276218611521369</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001440507058484575</v>
+        <v>0.001946328516661799</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.000943118184497449</v>
+        <v>0.001650456822870638</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.003137022787806998</v>
+        <v>0.005997045790251077</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.001635930993456247</v>
+        <v>0.00519020937776471</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.00308892355694228</v>
+        <v>0.001209082866411126</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.003715718077263286</v>
+        <v>0.003152885187388454</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.006107749927974637</v>
+        <v>0.004777351813624342</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.003521751997632372</v>
+        <v>0.004253420582986289</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001679929266136138</v>
+        <v>0.001591263650546015</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.005150976909413796</v>
+        <v>0.009908581539368955</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.0021899970405445</v>
+        <v>0.005797555625195849</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.007364462550924445</v>
+        <v>0.004230648699467232</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.008375110586847478</v>
+        <v>-0.001536189069423921</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.01579722959033298</v>
+        <v>0.01052166224580023</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.007822724568709083</v>
+        <v>0.004224519940915783</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.008930150309460616</v>
+        <v>0.003747769185008909</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.000407395800689403</v>
+        <v>0.0007800312012480326</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.00189069423929098</v>
+        <v>0.004785819793205292</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0159131469363474</v>
+        <v>0.01032143910350933</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.004697193500738528</v>
+        <v>0.005062166962699832</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.00669024462127904</v>
+        <v>0.01122900088417333</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001686889612311304</v>
+        <v>0.002820432466311485</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.00177847113884555</v>
+        <v>0.0004700720777185641</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0005954246317768197</v>
+        <v>0.001316201817612017</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0132036545829649</v>
+        <v>0.009725906277630435</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.01070791195716833</v>
+        <v>0.00683836589698047</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.001354076634975498</v>
+        <v>0.001506646971934999</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.003595638078396657</v>
+        <v>0.004865821291654415</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.005039787798408424</v>
+        <v>0.006427457098283929</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.00103153551429408</v>
+        <v>0.001568511393903493</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.001272565847883966</v>
+        <v>0.006912850812407645</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.009502664298401364</v>
+        <v>0.001598105948505479</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.00307113757442804</v>
+        <v>0.007785314066647053</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.008399646330680754</v>
+        <v>0.005809495723975266</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.001065975223278559</v>
+        <v>0.0006216696269982558</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.009702152757298688</v>
+        <v>0.008237129485179396</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.005148205928237115</v>
+        <v>0.004570923031554153</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.003601267646211437</v>
+        <v>0.002831023296962609</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.02291359480979055</v>
+        <v>0.02270716602772046</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.005012964563526323</v>
+        <v>0.002752293577981646</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.008209399167162401</v>
+        <v>0.006222353288115634</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0004033419763756485</v>
+        <v>0.0006864274570982598</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.005617977528089879</v>
+        <v>0.000374531835206049</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.002808112324492984</v>
+        <v>0.001091123562370999</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.240249609983373e-05</v>
+        <v>0.0002072232089994297</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.003457216940363006</v>
+        <v>0.002045520023048131</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.004350331316623435</v>
+        <v>0.01265113535830141</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>0.0001473622163277621</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001716068642745716</v>
+        <v>0.00214158239143365</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.005304212168486722</v>
+        <v>0.002633915359573824</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.00486739469578783</v>
+        <v>0.005042760247714595</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.00175741861135118</v>
+        <v>0.003111495246326745</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.004638432728320352</v>
+        <v>0.00566204659392513</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.01819032761310452</v>
+        <v>0.009790622235328861</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.005570291777188263</v>
+        <v>0.004293324976496382</v>
       </c>
     </row>
   </sheetData>
